--- a/DAISIES 2K26.xlsx
+++ b/DAISIES 2K26.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5bf0e59980aecf5/Becoming a Builder in 6 Months/Python/Excel to CSV Converter App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{586FB57B-E7AF-4125-9A76-A718C9B57D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{586FB57B-E7AF-4125-9A76-A718C9B57D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96B2D92-FDFC-404E-9865-58A457393DE4}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{C06728BB-D2BE-44E2-9413-FE7111D8B63D}"/>
+    <workbookView xWindow="3336" yWindow="2448" windowWidth="17280" windowHeight="8880" xr2:uid="{C06728BB-D2BE-44E2-9413-FE7111D8B63D}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall Plan" sheetId="1" r:id="rId1"/>
-    <sheet name="Cost Breakdown (Est)" sheetId="2" r:id="rId2"/>
-    <sheet name="Transport " sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Options</t>
   </si>
@@ -137,50 +135,13 @@
   </si>
   <si>
     <t>Rental Car</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Per Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accomodation (approx) </t>
-  </si>
-  <si>
-    <t>Total Per day</t>
-  </si>
-  <si>
-    <t>Grand total</t>
-  </si>
-  <si>
-    <t>Grand Total Per Person</t>
-  </si>
-  <si>
-    <t>Drive from Rondebosch to Yzterfontein and Back (2 hr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shuttle to and From Daisies </t>
-  </si>
-  <si>
-    <t>Commuting from Rondebosch to Daisies every day (1 hr 20 min)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R&quot;* #,##0.00_-;\-&quot;R&quot;* #,##0.00_-;_-&quot;R&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,7 +158,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,12 +168,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCE3C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -241,42 +196,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -624,246 +562,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="4" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="3"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D0B73D2-D1D7-4FAC-A7FC-2667C15AC88C}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="9">
-        <v>10000</v>
-      </c>
-      <c r="C2" s="9">
-        <f>B2/6</f>
-        <v>1666.6666666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6BFF8F-BE98-4F02-94A8-0A69495ADFBF}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
